--- a/output/customers.xlsx
+++ b/output/customers.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9B241F-95F4-46C9-B0CA-DBC3A7E21CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Customers" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Customers" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
     <t>Company Name</t>
   </si>
@@ -26,40 +22,36 @@
     <t>CC Email</t>
   </si>
   <si>
+    <t>Khushi jain's</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Preets' Store</t>
+  </si>
+  <si>
     <t>Tecnoprism</t>
   </si>
   <si>
-    <t>nihalsolanki654@gmail.com</t>
-  </si>
-  <si>
-    <t>solankinihal111@gmail.com</t>
+    <t>Test Sync Company 1771937935657</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -84,33 +76,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -447,9 +428,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="35" customWidth="1"/>
   </cols>
@@ -469,19 +450,48 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{D7D3152A-3B9A-43F1-AB9D-C1394604C8C4}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{90B43F6D-D3C2-4CAD-8BA7-C4F9480591C5}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/output/customers.xlsx
+++ b/output/customers.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEE75BE-DAAB-49A7-B5ED-FF537E9193B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Customers" state="visible" r:id="rId4"/>
+    <sheet name="Customers" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t>Company Name</t>
   </si>
@@ -35,23 +39,39 @@
   </si>
   <si>
     <t>Test Sync Company 1771937935657</t>
+  </si>
+  <si>
+    <t>khushijain11@gmail.com</t>
+  </si>
+  <si>
+    <t>khushi123@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,22 +96,33 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -428,9 +459,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35" customWidth="1"/>
   </cols>
@@ -450,11 +481,11 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -491,7 +522,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{BB8F6A35-4157-42C1-8336-E5CCD1977D57}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{83126327-654C-4A93-AFD9-A88AB3E800AA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>